--- a/src/xlsx/routes.xlsx
+++ b/src/xlsx/routes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bd6ffaf480ac5cc/Office/pokeredCHS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/Pokemon_Projects/pokeredCHS/src/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1941" documentId="11_A116FE3C5A3CB2768750E9EE180541CC1A3EF808" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED01DC4-D23D-E347-AE5C-0155CCD5E4B1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAD4B41-2169-A747-A5BB-D0E067A2F0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="760" windowWidth="23560" windowHeight="20480" firstSheet="29" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="760" windowWidth="23560" windowHeight="20480" firstSheet="47" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DiglettsCaveRoute2" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17628" uniqueCount="8340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17628" uniqueCount="8341">
   <si>
     <t>text/DiglettsCaveRoute2.asm</t>
   </si>
@@ -25424,6 +25424,10 @@
   </si>
   <si>
     <t>_Route8BattleText1::</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我才没有不甘心！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -84659,7 +84663,7 @@
         <v>520</v>
       </c>
       <c r="G93" t="s">
-        <v>7799</v>
+        <v>8340</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>7799</v>
